--- a/output/zone_monthly_4_02/renewable_installed_capacity_4_02.xlsx
+++ b/output/zone_monthly_4_02/renewable_installed_capacity_4_02.xlsx
@@ -4061,7 +4061,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>例如：全國、台電、民營電廠、自用發電設備、再生能源</t>
+          <t>例如：全國、台電、民營電廠、自用發電設備、再生能源、直轉供及躉售</t>
         </is>
       </c>
     </row>

--- a/output/zone_monthly_4_02/renewable_installed_capacity_4_02.xlsx
+++ b/output/zone_monthly_4_02/renewable_installed_capacity_4_02.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,67 +562,67 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21208.530361</v>
+        <v>21208.529881</v>
       </c>
       <c r="E2" t="n">
         <v>2122.6235</v>
       </c>
       <c r="F2" t="n">
-        <v>10.00834788582643</v>
+        <v>10.0083481123394</v>
       </c>
       <c r="G2" t="n">
         <v>7.489</v>
       </c>
       <c r="H2" t="n">
-        <v>0.035311263310217</v>
+        <v>0.035311264109396</v>
       </c>
       <c r="I2" t="n">
-        <v>14364.508161</v>
+        <v>14364.507681</v>
       </c>
       <c r="J2" t="n">
-        <v>67.7298611289665</v>
+        <v>67.72986039861573</v>
       </c>
       <c r="K2" t="n">
         <v>3963.4467</v>
       </c>
       <c r="L2" t="n">
-        <v>18.68798371474298</v>
+        <v>18.68798413769696</v>
       </c>
       <c r="M2" t="n">
         <v>936.6037</v>
       </c>
       <c r="N2" t="n">
-        <v>4.41616502443896</v>
+        <v>4.416165124387388</v>
       </c>
       <c r="O2" t="n">
         <v>3026.843</v>
       </c>
       <c r="P2" t="n">
-        <v>14.27181869030402</v>
+        <v>14.27181901330957</v>
       </c>
       <c r="Q2" t="n">
         <v>83.998</v>
       </c>
       <c r="R2" t="n">
-        <v>0.396057617242836</v>
+        <v>0.396057626206572</v>
       </c>
       <c r="S2" t="n">
         <v>61.452</v>
       </c>
       <c r="T2" t="n">
-        <v>0.289751335684263</v>
+        <v>0.289751342242032</v>
       </c>
       <c r="U2" t="n">
         <v>22.546</v>
       </c>
       <c r="V2" t="n">
-        <v>0.106306281558573</v>
+        <v>0.106306283964539</v>
       </c>
       <c r="W2" t="n">
         <v>666.465</v>
       </c>
       <c r="X2" t="n">
-        <v>3.142438389911029</v>
+        <v>3.142438461031961</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -645,67 +645,67 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21300.964566</v>
+        <v>21300.964256</v>
       </c>
       <c r="E3" t="n">
         <v>2122.6835</v>
       </c>
       <c r="F3" t="n">
-        <v>9.965198962812076</v>
+        <v>9.965199107838924</v>
       </c>
       <c r="G3" t="n">
         <v>7.489</v>
       </c>
       <c r="H3" t="n">
-        <v>0.035158032289081</v>
+        <v>0.035158032800748</v>
       </c>
       <c r="I3" t="n">
-        <v>14440.882366</v>
+        <v>14440.882056</v>
       </c>
       <c r="J3" t="n">
-        <v>67.79449973382955</v>
+        <v>67.79449926513223</v>
       </c>
       <c r="K3" t="n">
         <v>3979.4467</v>
       </c>
       <c r="L3" t="n">
-        <v>18.68200234627816</v>
+        <v>18.68200261816354</v>
       </c>
       <c r="M3" t="n">
         <v>936.6037</v>
       </c>
       <c r="N3" t="n">
-        <v>4.397001352206277</v>
+        <v>4.397001416197297</v>
       </c>
       <c r="O3" t="n">
         <v>3042.843</v>
       </c>
       <c r="P3" t="n">
-        <v>14.28500099407188</v>
+        <v>14.28500120196624</v>
       </c>
       <c r="Q3" t="n">
         <v>83.998</v>
       </c>
       <c r="R3" t="n">
-        <v>0.394338949955699</v>
+        <v>0.394338955694645</v>
       </c>
       <c r="S3" t="n">
         <v>61.452</v>
       </c>
       <c r="T3" t="n">
-        <v>0.288493977864683</v>
+        <v>0.288493982063232</v>
       </c>
       <c r="U3" t="n">
         <v>22.546</v>
       </c>
       <c r="V3" t="n">
-        <v>0.105844972091016</v>
+        <v>0.105844973631413</v>
       </c>
       <c r="W3" t="n">
         <v>666.465</v>
       </c>
       <c r="X3" t="n">
-        <v>3.128801974835415</v>
+        <v>3.128802020369909</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -728,67 +728,67 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21370.634421</v>
+        <v>21370.634111</v>
       </c>
       <c r="E4" t="n">
         <v>2122.2035</v>
       </c>
       <c r="F4" t="n">
-        <v>9.930465601501293</v>
+        <v>9.930465745551503</v>
       </c>
       <c r="G4" t="n">
         <v>7.489</v>
       </c>
       <c r="H4" t="n">
-        <v>0.035043414493305</v>
+        <v>0.035043415001641</v>
       </c>
       <c r="I4" t="n">
-        <v>14510.871121</v>
+        <v>14510.870811</v>
       </c>
       <c r="J4" t="n">
-        <v>67.90098429057771</v>
+        <v>67.900983824953</v>
       </c>
       <c r="K4" t="n">
         <v>3979.4128</v>
       </c>
       <c r="L4" t="n">
-        <v>18.62093900258573</v>
+        <v>18.62093927269896</v>
       </c>
       <c r="M4" t="n">
         <v>936.5698</v>
       </c>
       <c r="N4" t="n">
-        <v>4.382508172427831</v>
+        <v>4.382508235999998</v>
       </c>
       <c r="O4" t="n">
         <v>3042.843</v>
       </c>
       <c r="P4" t="n">
-        <v>14.2384308301579</v>
+        <v>14.23843103669896</v>
       </c>
       <c r="Q4" t="n">
         <v>84.193</v>
       </c>
       <c r="R4" t="n">
-        <v>0.393965842760696</v>
+        <v>0.39396584847552</v>
       </c>
       <c r="S4" t="n">
         <v>61.452</v>
       </c>
       <c r="T4" t="n">
-        <v>0.287553466075924</v>
+        <v>0.287553470247142</v>
       </c>
       <c r="U4" t="n">
         <v>22.741</v>
       </c>
       <c r="V4" t="n">
-        <v>0.106412376684772</v>
+        <v>0.106412378228378</v>
       </c>
       <c r="W4" t="n">
         <v>666.465</v>
       </c>
       <c r="X4" t="n">
-        <v>3.11860184808128</v>
+        <v>3.118601893319365</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -811,67 +811,67 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21483.813576</v>
+        <v>21482.158266</v>
       </c>
       <c r="E5" t="n">
-        <v>2123.8595</v>
+        <v>2122.2035</v>
       </c>
       <c r="F5" t="n">
-        <v>9.885858916466331</v>
+        <v>9.878911949731004</v>
       </c>
       <c r="G5" t="n">
         <v>7.489</v>
       </c>
       <c r="H5" t="n">
-        <v>0.034858801830072</v>
+        <v>0.034861487878771</v>
       </c>
       <c r="I5" t="n">
-        <v>14622.394276</v>
+        <v>14622.394966</v>
       </c>
       <c r="J5" t="n">
-        <v>68.06237739995552</v>
+        <v>68.06762516568456</v>
       </c>
       <c r="K5" t="n">
         <v>3979.4128</v>
       </c>
       <c r="L5" t="n">
-        <v>18.52284179399826</v>
+        <v>18.52426907355138</v>
       </c>
       <c r="M5" t="n">
         <v>936.5698</v>
       </c>
       <c r="N5" t="n">
-        <v>4.359420624680252</v>
+        <v>4.359756540302179</v>
       </c>
       <c r="O5" t="n">
         <v>3042.843</v>
       </c>
       <c r="P5" t="n">
-        <v>14.163421169318</v>
+        <v>14.16451253324921</v>
       </c>
       <c r="Q5" t="n">
         <v>84.193</v>
       </c>
       <c r="R5" t="n">
-        <v>0.391890386230374</v>
+        <v>0.391920583385949</v>
       </c>
       <c r="S5" t="n">
         <v>61.452</v>
       </c>
       <c r="T5" t="n">
-        <v>0.286038601957751</v>
+        <v>0.286060642692781</v>
       </c>
       <c r="U5" t="n">
         <v>22.741</v>
       </c>
       <c r="V5" t="n">
-        <v>0.105851784272623</v>
+        <v>0.105859940693168</v>
       </c>
       <c r="W5" t="n">
         <v>666.465</v>
       </c>
       <c r="X5" t="n">
-        <v>3.102172701519443</v>
+        <v>3.102411739768346</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -894,67 +894,67 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21555.032906</v>
+        <v>21589.038266</v>
       </c>
       <c r="E6" t="n">
         <v>2123.8595</v>
       </c>
       <c r="F6" t="n">
-        <v>9.853195350069766</v>
+        <v>9.837675369471228</v>
       </c>
       <c r="G6" t="n">
         <v>7.489</v>
       </c>
       <c r="H6" t="n">
-        <v>0.034743625920958</v>
+        <v>0.034688900486106</v>
       </c>
       <c r="I6" t="n">
-        <v>14693.632606</v>
+        <v>14727.637966</v>
       </c>
       <c r="J6" t="n">
-        <v>68.16798967590498</v>
+        <v>68.21812896220653</v>
       </c>
       <c r="K6" t="n">
         <v>3979.4128</v>
       </c>
       <c r="L6" t="n">
-        <v>18.46164103462027</v>
+        <v>18.43256170547935</v>
       </c>
       <c r="M6" t="n">
         <v>936.5698</v>
       </c>
       <c r="N6" t="n">
-        <v>4.345016795308621</v>
+        <v>4.338172865601794</v>
       </c>
       <c r="O6" t="n">
         <v>3042.843</v>
       </c>
       <c r="P6" t="n">
-        <v>14.11662423931166</v>
+        <v>14.09438883987756</v>
       </c>
       <c r="Q6" t="n">
         <v>84.17400000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0.390507406632488</v>
+        <v>0.389892309990313</v>
       </c>
       <c r="S6" t="n">
         <v>61.452</v>
       </c>
       <c r="T6" t="n">
-        <v>0.285093510494685</v>
+        <v>0.284644453554835</v>
       </c>
       <c r="U6" t="n">
         <v>22.722</v>
       </c>
       <c r="V6" t="n">
-        <v>0.105413896137803</v>
+        <v>0.105247856435478</v>
       </c>
       <c r="W6" t="n">
         <v>666.465</v>
       </c>
       <c r="X6" t="n">
-        <v>3.091922906851535</v>
+        <v>3.087052752366455</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -977,67 +977,67 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21702.836266</v>
+        <v>21704.240786</v>
       </c>
       <c r="E7" t="n">
         <v>2123.8595</v>
       </c>
       <c r="F7" t="n">
-        <v>9.786091891257877</v>
+        <v>9.785458615857063</v>
       </c>
       <c r="G7" t="n">
         <v>7.489</v>
       </c>
       <c r="H7" t="n">
-        <v>0.034507010550194</v>
+        <v>0.034504777540206</v>
       </c>
       <c r="I7" t="n">
-        <v>14842.945566</v>
+        <v>14844.350086</v>
       </c>
       <c r="J7" t="n">
-        <v>68.39173177218863</v>
+        <v>68.39377719940855</v>
       </c>
       <c r="K7" t="n">
         <v>3977.9032</v>
       </c>
       <c r="L7" t="n">
-        <v>18.32895549339717</v>
+        <v>18.32776939410794</v>
       </c>
       <c r="M7" t="n">
         <v>935.0602</v>
       </c>
       <c r="N7" t="n">
-        <v>4.308470047598708</v>
+        <v>4.308191238843731</v>
       </c>
       <c r="O7" t="n">
         <v>3042.843</v>
       </c>
       <c r="P7" t="n">
-        <v>14.02048544579846</v>
+        <v>14.0195781552642</v>
       </c>
       <c r="Q7" t="n">
         <v>84.17400000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>0.387847924429436</v>
+        <v>0.387822826100857</v>
       </c>
       <c r="S7" t="n">
         <v>61.452</v>
       </c>
       <c r="T7" t="n">
-        <v>0.283151931143081</v>
+        <v>0.283133607878322</v>
       </c>
       <c r="U7" t="n">
         <v>22.722</v>
       </c>
       <c r="V7" t="n">
-        <v>0.104695993286355</v>
+        <v>0.104689218222535</v>
       </c>
       <c r="W7" t="n">
         <v>666.465</v>
       </c>
       <c r="X7" t="n">
-        <v>3.070865908176686</v>
+        <v>3.070667186985381</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1060,67 +1060,67 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21884.710151</v>
+        <v>21886.610831</v>
       </c>
       <c r="E8" t="n">
         <v>2123.8595</v>
       </c>
       <c r="F8" t="n">
-        <v>9.704764126852977</v>
+        <v>9.703921344422064</v>
       </c>
       <c r="G8" t="n">
         <v>7.489</v>
       </c>
       <c r="H8" t="n">
-        <v>0.034220238460219</v>
+        <v>0.034217266701671</v>
       </c>
       <c r="I8" t="n">
-        <v>14940.724451</v>
+        <v>14942.625131</v>
       </c>
       <c r="J8" t="n">
-        <v>68.27015001757883</v>
+        <v>68.27290550547644</v>
       </c>
       <c r="K8" t="n">
         <v>4061.9482</v>
       </c>
       <c r="L8" t="n">
-        <v>18.56066711404169</v>
+        <v>18.55905526609306</v>
       </c>
       <c r="M8" t="n">
         <v>935.0602</v>
       </c>
       <c r="N8" t="n">
-        <v>4.272664310142912</v>
+        <v>4.272293262854517</v>
       </c>
       <c r="O8" t="n">
         <v>3126.888</v>
       </c>
       <c r="P8" t="n">
-        <v>14.28800280389878</v>
+        <v>14.28676200323855</v>
       </c>
       <c r="Q8" t="n">
         <v>84.224</v>
       </c>
       <c r="R8" t="n">
-        <v>0.384853166520697</v>
+        <v>0.384819745050275</v>
       </c>
       <c r="S8" t="n">
         <v>61.452</v>
       </c>
       <c r="T8" t="n">
-        <v>0.28079878406428</v>
+        <v>0.280774398898526</v>
       </c>
       <c r="U8" t="n">
         <v>22.772</v>
       </c>
       <c r="V8" t="n">
-        <v>0.104054382456418</v>
+        <v>0.104045346151748</v>
       </c>
       <c r="W8" t="n">
         <v>666.465</v>
       </c>
       <c r="X8" t="n">
-        <v>3.0453453365456</v>
+        <v>3.045080872256499</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1143,67 +1143,67 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22031.523171</v>
+        <v>22030.938291</v>
       </c>
       <c r="E9" t="n">
         <v>2123.8595</v>
       </c>
       <c r="F9" t="n">
-        <v>9.640093803389986</v>
+        <v>9.640349729759953</v>
       </c>
       <c r="G9" t="n">
         <v>7.489</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03399220263562</v>
+        <v>0.033993105064705</v>
       </c>
       <c r="I9" t="n">
-        <v>15019.677471</v>
+        <v>15019.092591</v>
       </c>
       <c r="J9" t="n">
-        <v>68.17357726210386</v>
+        <v>68.1727323304044</v>
       </c>
       <c r="K9" t="n">
         <v>4129.5482</v>
       </c>
       <c r="L9" t="n">
-        <v>18.74381615809345</v>
+        <v>18.74431377117963</v>
       </c>
       <c r="M9" t="n">
         <v>932.6602</v>
       </c>
       <c r="N9" t="n">
-        <v>4.233298772677037</v>
+        <v>4.233411158802106</v>
       </c>
       <c r="O9" t="n">
         <v>3196.888</v>
       </c>
       <c r="P9" t="n">
-        <v>14.51051738541641</v>
+        <v>14.51090261237753</v>
       </c>
       <c r="Q9" t="n">
         <v>84.48399999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>0.383468720452365</v>
+        <v>0.383478900826086</v>
       </c>
       <c r="S9" t="n">
         <v>61.452</v>
       </c>
       <c r="T9" t="n">
-        <v>0.27892760533638</v>
+        <v>0.278935010340001</v>
       </c>
       <c r="U9" t="n">
         <v>23.032</v>
       </c>
       <c r="V9" t="n">
-        <v>0.104541115115985</v>
+        <v>0.104543890486085</v>
       </c>
       <c r="W9" t="n">
         <v>666.465</v>
       </c>
       <c r="X9" t="n">
-        <v>3.025051853324717</v>
+        <v>3.025132162765224</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1226,67 +1226,67 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22192.107191</v>
+        <v>22192.106751</v>
       </c>
       <c r="E10" t="n">
         <v>2123.8595</v>
       </c>
       <c r="F10" t="n">
-        <v>9.570337245222618</v>
+        <v>9.570337434972446</v>
       </c>
       <c r="G10" t="n">
         <v>7.489</v>
       </c>
       <c r="H10" t="n">
-        <v>0.033746232097496</v>
+        <v>0.033746232766578</v>
       </c>
       <c r="I10" t="n">
-        <v>15098.769491</v>
+        <v>15098.769051</v>
       </c>
       <c r="J10" t="n">
-        <v>68.03666439175862</v>
+        <v>68.03666375802574</v>
       </c>
       <c r="K10" t="n">
         <v>4213.0602</v>
       </c>
       <c r="L10" t="n">
-        <v>18.98449824408114</v>
+        <v>18.98449862048431</v>
       </c>
       <c r="M10" t="n">
         <v>932.6602</v>
       </c>
       <c r="N10" t="n">
-        <v>4.202666254145708</v>
+        <v>4.202666337471423</v>
       </c>
       <c r="O10" t="n">
         <v>3280.4</v>
       </c>
       <c r="P10" t="n">
-        <v>14.78183198993543</v>
+        <v>14.78183228301289</v>
       </c>
       <c r="Q10" t="n">
         <v>84.434</v>
       </c>
       <c r="R10" t="n">
-        <v>0.380468602072372</v>
+        <v>0.380468609615873</v>
       </c>
       <c r="S10" t="n">
         <v>61.452</v>
       </c>
       <c r="T10" t="n">
-        <v>0.276909260896693</v>
+        <v>0.276909266386937</v>
       </c>
       <c r="U10" t="n">
         <v>22.982</v>
       </c>
       <c r="V10" t="n">
-        <v>0.103559341175679</v>
+        <v>0.103559343228936</v>
       </c>
       <c r="W10" t="n">
         <v>664.495</v>
       </c>
       <c r="X10" t="n">
-        <v>2.994285284767756</v>
+        <v>2.994285344135059</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1309,67 +1309,67 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>22344.513061</v>
+        <v>22344.512741</v>
       </c>
       <c r="E11" t="n">
         <v>2123.8595</v>
       </c>
       <c r="F11" t="n">
-        <v>9.505060567674548</v>
+        <v>9.505060703798321</v>
       </c>
       <c r="G11" t="n">
         <v>7.489</v>
       </c>
       <c r="H11" t="n">
-        <v>0.033516058190909</v>
+        <v>0.033516058670899</v>
       </c>
       <c r="I11" t="n">
-        <v>15183.575361</v>
+        <v>15183.575041</v>
       </c>
       <c r="J11" t="n">
-        <v>67.95214252174209</v>
+        <v>67.95214206277868</v>
       </c>
       <c r="K11" t="n">
         <v>4280.6602</v>
       </c>
       <c r="L11" t="n">
-        <v>19.15754524752407</v>
+        <v>19.15754552188291</v>
       </c>
       <c r="M11" t="n">
         <v>930.2602000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>4.163260114285827</v>
+        <v>4.163260173908664</v>
       </c>
       <c r="O11" t="n">
         <v>3350.4</v>
       </c>
       <c r="P11" t="n">
-        <v>14.99428513323824</v>
+        <v>14.99428534797424</v>
       </c>
       <c r="Q11" t="n">
         <v>84.434</v>
       </c>
       <c r="R11" t="n">
-        <v>0.377873528814421</v>
+        <v>0.37787353422602</v>
       </c>
       <c r="S11" t="n">
         <v>61.452</v>
       </c>
       <c r="T11" t="n">
-        <v>0.275020537848542</v>
+        <v>0.275020541787164</v>
       </c>
       <c r="U11" t="n">
         <v>22.982</v>
       </c>
       <c r="V11" t="n">
-        <v>0.102852990965879</v>
+        <v>0.102852992438856</v>
       </c>
       <c r="W11" t="n">
         <v>664.495</v>
       </c>
       <c r="X11" t="n">
-        <v>2.973862076053947</v>
+        <v>2.97386211864319</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1392,67 +1392,67 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>22466.793341</v>
+        <v>22466.793021</v>
       </c>
       <c r="E12" t="n">
         <v>2124.4215</v>
       </c>
       <c r="F12" t="n">
-        <v>9.455828732456936</v>
+        <v>9.455828867138607</v>
       </c>
       <c r="G12" t="n">
         <v>7.489</v>
       </c>
       <c r="H12" t="n">
-        <v>0.033333639947332</v>
+        <v>0.033333640422111</v>
       </c>
       <c r="I12" t="n">
-        <v>15263.537641</v>
+        <v>15263.537321</v>
       </c>
       <c r="J12" t="n">
-        <v>67.93821178363417</v>
+        <v>67.93821132697032</v>
       </c>
       <c r="K12" t="n">
         <v>4322.4162</v>
       </c>
       <c r="L12" t="n">
-        <v>19.2391327698375</v>
+        <v>19.23913304386515</v>
       </c>
       <c r="M12" t="n">
         <v>930.2602000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>4.140600689562377</v>
+        <v>4.140600748537959</v>
       </c>
       <c r="O12" t="n">
         <v>3392.156</v>
       </c>
       <c r="P12" t="n">
-        <v>15.09853208027512</v>
+        <v>15.09853229532719</v>
       </c>
       <c r="Q12" t="n">
         <v>84.434</v>
       </c>
       <c r="R12" t="n">
-        <v>0.375816872120843</v>
+        <v>0.375816877473694</v>
       </c>
       <c r="S12" t="n">
         <v>61.452</v>
       </c>
       <c r="T12" t="n">
-        <v>0.27352368033695</v>
+        <v>0.273523684232814</v>
       </c>
       <c r="U12" t="n">
         <v>22.982</v>
       </c>
       <c r="V12" t="n">
-        <v>0.102293191783893</v>
+        <v>0.10229319324088</v>
       </c>
       <c r="W12" t="n">
         <v>664.495</v>
       </c>
       <c r="X12" t="n">
-        <v>2.957676202003215</v>
+        <v>2.957676244130117</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1475,67 +1475,67 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>22872.010996</v>
+        <v>22872.010676</v>
       </c>
       <c r="E13" t="n">
         <v>2124.4215</v>
       </c>
       <c r="F13" t="n">
-        <v>9.288302197701514</v>
+        <v>9.288302327653216</v>
       </c>
       <c r="G13" t="n">
         <v>7.489</v>
       </c>
       <c r="H13" t="n">
-        <v>0.032743076248563</v>
+        <v>0.032743076706668</v>
       </c>
       <c r="I13" t="n">
-        <v>15474.020296</v>
+        <v>15474.019976</v>
       </c>
       <c r="J13" t="n">
-        <v>67.65483060805713</v>
+        <v>67.65483015551912</v>
       </c>
       <c r="K13" t="n">
         <v>4517.1962</v>
       </c>
       <c r="L13" t="n">
-        <v>19.74988644763242</v>
+        <v>19.74988672395109</v>
       </c>
       <c r="M13" t="n">
         <v>930.2602000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>4.06724271058933</v>
+        <v>4.067242767493714</v>
       </c>
       <c r="O13" t="n">
         <v>3586.936</v>
       </c>
       <c r="P13" t="n">
-        <v>15.68264373704309</v>
+        <v>15.68264395645738</v>
       </c>
       <c r="Q13" t="n">
         <v>84.389</v>
       </c>
       <c r="R13" t="n">
-        <v>0.368961872284682</v>
+        <v>0.368961877446791</v>
       </c>
       <c r="S13" t="n">
         <v>61.452</v>
       </c>
       <c r="T13" t="n">
-        <v>0.268677730221217</v>
+        <v>0.26867773398026</v>
       </c>
       <c r="U13" t="n">
         <v>22.937</v>
       </c>
       <c r="V13" t="n">
-        <v>0.100284142063465</v>
+        <v>0.10028414346653</v>
       </c>
       <c r="W13" t="n">
         <v>664.495</v>
       </c>
       <c r="X13" t="n">
-        <v>2.905275798075696</v>
+        <v>2.905275838723118</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -1787,6 +1787,89 @@
         <v>2.826634886270485</v>
       </c>
       <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>再生能源</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>04月</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>23733.114656</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2124.7865</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8.952834597555993</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12.937</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.054510333715214</v>
+      </c>
+      <c r="I17" t="n">
+        <v>15836.692956</v>
+      </c>
+      <c r="J17" t="n">
+        <v>66.72825368918151</v>
+      </c>
+      <c r="K17" t="n">
+        <v>5014.4722</v>
+      </c>
+      <c r="L17" t="n">
+        <v>21.1285887785162</v>
+      </c>
+      <c r="M17" t="n">
+        <v>940.2202</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.961638468561907</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4074.252</v>
+      </c>
+      <c r="P17" t="n">
+        <v>17.16695030995429</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>79.73099999999999</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.335948320124274</v>
+      </c>
+      <c r="S17" t="n">
+        <v>61.452</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.258929352049729</v>
+      </c>
+      <c r="U17" t="n">
+        <v>18.279</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.077018968074546</v>
+      </c>
+      <c r="W17" t="n">
+        <v>664.495</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.799864280906796</v>
+      </c>
+      <c r="Y17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3442,67 +3525,67 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>22872.010996</v>
+        <v>22872.010676</v>
       </c>
       <c r="E20" t="n">
         <v>2124.4215</v>
       </c>
       <c r="F20" t="n">
-        <v>9.288302197701514</v>
+        <v>9.288302327653216</v>
       </c>
       <c r="G20" t="n">
         <v>7.489</v>
       </c>
       <c r="H20" t="n">
-        <v>0.032743076248563</v>
+        <v>0.032743076706668</v>
       </c>
       <c r="I20" t="n">
-        <v>15474.020296</v>
+        <v>15474.019976</v>
       </c>
       <c r="J20" t="n">
-        <v>67.65483060805713</v>
+        <v>67.65483015551912</v>
       </c>
       <c r="K20" t="n">
         <v>4517.1962</v>
       </c>
       <c r="L20" t="n">
-        <v>19.74988644763242</v>
+        <v>19.74988672395109</v>
       </c>
       <c r="M20" t="n">
         <v>930.2602000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>4.06724271058933</v>
+        <v>4.067242767493714</v>
       </c>
       <c r="O20" t="n">
         <v>3586.936</v>
       </c>
       <c r="P20" t="n">
-        <v>15.68264373704309</v>
+        <v>15.68264395645738</v>
       </c>
       <c r="Q20" t="n">
         <v>84.389</v>
       </c>
       <c r="R20" t="n">
-        <v>0.368961872284682</v>
+        <v>0.368961877446791</v>
       </c>
       <c r="S20" t="n">
         <v>61.452</v>
       </c>
       <c r="T20" t="n">
-        <v>0.268677730221217</v>
+        <v>0.26867773398026</v>
       </c>
       <c r="U20" t="n">
         <v>22.937</v>
       </c>
       <c r="V20" t="n">
-        <v>0.100284142063465</v>
+        <v>0.10028414346653</v>
       </c>
       <c r="W20" t="n">
         <v>664.495</v>
       </c>
       <c r="X20" t="n">
-        <v>2.905275798075696</v>
+        <v>2.905275838723118</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>

--- a/output/zone_monthly_4_02/renewable_installed_capacity_4_02.xlsx
+++ b/output/zone_monthly_4_02/renewable_installed_capacity_4_02.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1870,6 +1870,89 @@
         <v>2.799864280906796</v>
       </c>
       <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>再生能源</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>05月</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>24007.615931</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2124.7865</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8.850468560088697</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12.937</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.053887066659105</v>
+      </c>
+      <c r="I18" t="n">
+        <v>15914.412231</v>
+      </c>
+      <c r="J18" t="n">
+        <v>66.28901543884832</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5195.9842</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.64306616256156</v>
+      </c>
+      <c r="M18" t="n">
+        <v>940.2202</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.916341392257672</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4255.764</v>
+      </c>
+      <c r="P18" t="n">
+        <v>17.72672477030389</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>79.501</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.331149082976389</v>
+      </c>
+      <c r="S18" t="n">
+        <v>61.452</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.255968773311846</v>
+      </c>
+      <c r="U18" t="n">
+        <v>18.049</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.075180309664543</v>
+      </c>
+      <c r="W18" t="n">
+        <v>679.995</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.832413688865923</v>
+      </c>
+      <c r="Y18" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/zone_monthly_4_02/renewable_installed_capacity_4_02.xlsx
+++ b/output/zone_monthly_4_02/renewable_installed_capacity_4_02.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1953,6 +1953,89 @@
         <v>2.832413688865923</v>
       </c>
       <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>再生能源</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>06月</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>24317.236601</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2124.7865</v>
+      </c>
+      <c r="F19" t="n">
+        <v>8.737779439595624</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12.937</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.053200946358633</v>
+      </c>
+      <c r="I19" t="n">
+        <v>15999.457901</v>
+      </c>
+      <c r="J19" t="n">
+        <v>65.79472068936505</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5419.9842</v>
+      </c>
+      <c r="L19" t="n">
+        <v>22.28865182722741</v>
+      </c>
+      <c r="M19" t="n">
+        <v>940.2202</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.866476341153563</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4479.764</v>
+      </c>
+      <c r="P19" t="n">
+        <v>18.42217548607385</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>80.07599999999999</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.329297285353168</v>
+      </c>
+      <c r="S19" t="n">
+        <v>61.452</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.252709635590225</v>
+      </c>
+      <c r="U19" t="n">
+        <v>18.624</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.07658764976294299</v>
+      </c>
+      <c r="W19" t="n">
+        <v>679.995</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.796349812100099</v>
+      </c>
+      <c r="Y19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1967,7 +2050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,1622 +2179,6 @@
           <t>solar_water_heater_area_1000m2</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>96年</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2818.922</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1921.25</v>
-      </c>
-      <c r="F2" t="n">
-        <v>68.15548638805899</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.086557911144757</v>
-      </c>
-      <c r="K2" t="n">
-        <v>185.99</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6.597912251562832</v>
-      </c>
-      <c r="M2" t="n">
-        <v>185.99</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6.597912251562832</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>86.78</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3.078481774238521</v>
-      </c>
-      <c r="S2" t="n">
-        <v>73.17</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.595673097730267</v>
-      </c>
-      <c r="U2" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.482808676508254</v>
-      </c>
-      <c r="W2" t="n">
-        <v>622.462</v>
-      </c>
-      <c r="X2" t="n">
-        <v>22.08156167499491</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>682.492</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>97年</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2903.166</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1937.954</v>
-      </c>
-      <c r="F3" t="n">
-        <v>66.75312400324336</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.192203959401564</v>
-      </c>
-      <c r="K3" t="n">
-        <v>250.39</v>
-      </c>
-      <c r="L3" t="n">
-        <v>8.624722113719987</v>
-      </c>
-      <c r="M3" t="n">
-        <v>250.39</v>
-      </c>
-      <c r="N3" t="n">
-        <v>8.624722113719987</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>86.78</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.989150465388476</v>
-      </c>
-      <c r="S3" t="n">
-        <v>73.17</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.520351919249536</v>
-      </c>
-      <c r="U3" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.468798546138939</v>
-      </c>
-      <c r="W3" t="n">
-        <v>622.462</v>
-      </c>
-      <c r="X3" t="n">
-        <v>21.44079945824662</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>800.254</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>98年</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>3029.996</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1936.954</v>
-      </c>
-      <c r="F4" t="n">
-        <v>63.92595897816367</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.313861800477624</v>
-      </c>
-      <c r="K4" t="n">
-        <v>374.29</v>
-      </c>
-      <c r="L4" t="n">
-        <v>12.35282158788329</v>
-      </c>
-      <c r="M4" t="n">
-        <v>374.29</v>
-      </c>
-      <c r="N4" t="n">
-        <v>12.35282158788329</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>86.78</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.864030183538197</v>
-      </c>
-      <c r="S4" t="n">
-        <v>73.17</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.414854673075476</v>
-      </c>
-      <c r="U4" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.44917551046272</v>
-      </c>
-      <c r="W4" t="n">
-        <v>622.462</v>
-      </c>
-      <c r="X4" t="n">
-        <v>20.54332744993723</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>900.032</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>99年</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>3197.141</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1977.454</v>
-      </c>
-      <c r="F5" t="n">
-        <v>61.8506972323085</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>34.555</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.080809385635479</v>
-      </c>
-      <c r="K5" t="n">
-        <v>475.89</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14.88486119317228</v>
-      </c>
-      <c r="M5" t="n">
-        <v>475.89</v>
-      </c>
-      <c r="N5" t="n">
-        <v>14.88486119317228</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>86.78</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.714300057457585</v>
-      </c>
-      <c r="S5" t="n">
-        <v>73.17</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.288607227519837</v>
-      </c>
-      <c r="U5" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.425692829937747</v>
-      </c>
-      <c r="W5" t="n">
-        <v>622.462</v>
-      </c>
-      <c r="X5" t="n">
-        <v>19.46933213142617</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1036.304</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>100年</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3399.124</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2040.754</v>
-      </c>
-      <c r="F6" t="n">
-        <v>60.03764499323944</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>129.912</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.821925884433755</v>
-      </c>
-      <c r="K6" t="n">
-        <v>522.6900000000001</v>
-      </c>
-      <c r="L6" t="n">
-        <v>15.37719718374499</v>
-      </c>
-      <c r="M6" t="n">
-        <v>522.6900000000001</v>
-      </c>
-      <c r="N6" t="n">
-        <v>15.37719718374499</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>81.336</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.392851805347496</v>
-      </c>
-      <c r="S6" t="n">
-        <v>73.17</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.15261343805051</v>
-      </c>
-      <c r="U6" t="n">
-        <v>8.166</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.240238367296986</v>
-      </c>
-      <c r="W6" t="n">
-        <v>624.432</v>
-      </c>
-      <c r="X6" t="n">
-        <v>18.37038013323433</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1156.71</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>101年</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>3594.01</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2081.271</v>
-      </c>
-      <c r="F7" t="n">
-        <v>57.90943820412297</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>231.281</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6.435179646133428</v>
-      </c>
-      <c r="K7" t="n">
-        <v>570.99</v>
-      </c>
-      <c r="L7" t="n">
-        <v>15.88726798200339</v>
-      </c>
-      <c r="M7" t="n">
-        <v>570.99</v>
-      </c>
-      <c r="N7" t="n">
-        <v>15.88726798200339</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>81.336</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.263098878411579</v>
-      </c>
-      <c r="S7" t="n">
-        <v>73.17</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.035887490574595</v>
-      </c>
-      <c r="U7" t="n">
-        <v>8.166</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.227211387836984</v>
-      </c>
-      <c r="W7" t="n">
-        <v>629.1319999999999</v>
-      </c>
-      <c r="X7" t="n">
-        <v>17.50501528932864</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1278.422</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>102年</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>3815.867</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2081.271</v>
-      </c>
-      <c r="F8" t="n">
-        <v>54.54254563903827</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>409.938</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10.74298449081166</v>
-      </c>
-      <c r="K8" t="n">
-        <v>614.1900000000001</v>
-      </c>
-      <c r="L8" t="n">
-        <v>16.09568677315011</v>
-      </c>
-      <c r="M8" t="n">
-        <v>614.1900000000001</v>
-      </c>
-      <c r="N8" t="n">
-        <v>16.09568677315011</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>81.336</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.1315208313078</v>
-      </c>
-      <c r="S8" t="n">
-        <v>73.17</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.917519661979833</v>
-      </c>
-      <c r="U8" t="n">
-        <v>8.166</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0.214001169327967</v>
-      </c>
-      <c r="W8" t="n">
-        <v>629.1319999999999</v>
-      </c>
-      <c r="X8" t="n">
-        <v>16.48726226569218</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1388.171</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>103年</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>4064.88</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2081.271</v>
-      </c>
-      <c r="F9" t="n">
-        <v>51.20129007498377</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>635.951</v>
-      </c>
-      <c r="J9" t="n">
-        <v>15.64501289090945</v>
-      </c>
-      <c r="K9" t="n">
-        <v>637.1900000000001</v>
-      </c>
-      <c r="L9" t="n">
-        <v>15.67549349550294</v>
-      </c>
-      <c r="M9" t="n">
-        <v>637.1900000000001</v>
-      </c>
-      <c r="N9" t="n">
-        <v>15.67549349550294</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>81.336</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.000944677333648</v>
-      </c>
-      <c r="S9" t="n">
-        <v>73.17</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.800053138100018</v>
-      </c>
-      <c r="U9" t="n">
-        <v>8.166</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.200891539233631</v>
-      </c>
-      <c r="W9" t="n">
-        <v>629.1319999999999</v>
-      </c>
-      <c r="X9" t="n">
-        <v>15.4772588612702</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1504.541</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>104年</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4329.358</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2089.271</v>
-      </c>
-      <c r="F10" t="n">
-        <v>48.25821750014667</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>884.251</v>
-      </c>
-      <c r="J10" t="n">
-        <v>20.42452945679244</v>
-      </c>
-      <c r="K10" t="n">
-        <v>646.6900000000001</v>
-      </c>
-      <c r="L10" t="n">
-        <v>14.93731865094086</v>
-      </c>
-      <c r="M10" t="n">
-        <v>646.6900000000001</v>
-      </c>
-      <c r="N10" t="n">
-        <v>14.93731865094086</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>80.014</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.84817240801061</v>
-      </c>
-      <c r="S10" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.632343640789235</v>
-      </c>
-      <c r="U10" t="n">
-        <v>9.343999999999999</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0.215828767221376</v>
-      </c>
-      <c r="W10" t="n">
-        <v>629.1319999999999</v>
-      </c>
-      <c r="X10" t="n">
-        <v>14.53176198410942</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1620.046</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>105年</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4725.562</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2089.271</v>
-      </c>
-      <c r="F11" t="n">
-        <v>44.21211699264553</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1245.055</v>
-      </c>
-      <c r="J11" t="n">
-        <v>26.34723658265408</v>
-      </c>
-      <c r="K11" t="n">
-        <v>682.09</v>
-      </c>
-      <c r="L11" t="n">
-        <v>14.43405038384853</v>
-      </c>
-      <c r="M11" t="n">
-        <v>682.09</v>
-      </c>
-      <c r="N11" t="n">
-        <v>14.43405038384853</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>80.014</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.69321659519016</v>
-      </c>
-      <c r="S11" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.495483500163578</v>
-      </c>
-      <c r="U11" t="n">
-        <v>9.343999999999999</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.197733095026581</v>
-      </c>
-      <c r="W11" t="n">
-        <v>629.1319999999999</v>
-      </c>
-      <c r="X11" t="n">
-        <v>13.3133794456617</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1715.647</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>106年</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>5258.509</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2089.271</v>
-      </c>
-      <c r="F12" t="n">
-        <v>39.73124320981479</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1767.702</v>
-      </c>
-      <c r="J12" t="n">
-        <v>33.61603070376032</v>
-      </c>
-      <c r="K12" t="n">
-        <v>692.39</v>
-      </c>
-      <c r="L12" t="n">
-        <v>13.16704031503987</v>
-      </c>
-      <c r="M12" t="n">
-        <v>684.39</v>
-      </c>
-      <c r="N12" t="n">
-        <v>13.01490593626444</v>
-      </c>
-      <c r="O12" t="n">
-        <v>8</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.152134378775429</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>80.014</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.521610022917143</v>
-      </c>
-      <c r="S12" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.343917068507442</v>
-      </c>
-      <c r="U12" t="n">
-        <v>9.343999999999999</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0.177692954409701</v>
-      </c>
-      <c r="W12" t="n">
-        <v>629.1319999999999</v>
-      </c>
-      <c r="X12" t="n">
-        <v>11.96407574846787</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1813.283</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>107年</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>6255.32637</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2091.467</v>
-      </c>
-      <c r="F13" t="n">
-        <v>33.43497806973739</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.0004795912831</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2738.11917</v>
-      </c>
-      <c r="J13" t="n">
-        <v>43.77260286740243</v>
-      </c>
-      <c r="K13" t="n">
-        <v>713.1512</v>
-      </c>
-      <c r="L13" t="n">
-        <v>11.40070330175274</v>
-      </c>
-      <c r="M13" t="n">
-        <v>705.1512</v>
-      </c>
-      <c r="N13" t="n">
-        <v>11.27281229292597</v>
-      </c>
-      <c r="O13" t="n">
-        <v>8</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.12789100882677</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>80.629</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.288965518836709</v>
-      </c>
-      <c r="S13" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.129757199223484</v>
-      </c>
-      <c r="U13" t="n">
-        <v>9.959</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.159208319613226</v>
-      </c>
-      <c r="W13" t="n">
-        <v>631.9299999999999</v>
-      </c>
-      <c r="X13" t="n">
-        <v>10.10227065098763</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1852.948</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>108年</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>7798.39143</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2092.467</v>
-      </c>
-      <c r="F14" t="n">
-        <v>26.83203348770607</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.003846947190236</v>
-      </c>
-      <c r="I14" t="n">
-        <v>4149.53943</v>
-      </c>
-      <c r="J14" t="n">
-        <v>53.21019683670841</v>
-      </c>
-      <c r="K14" t="n">
-        <v>845.159</v>
-      </c>
-      <c r="L14" t="n">
-        <v>10.83760680117592</v>
-      </c>
-      <c r="M14" t="n">
-        <v>717.159</v>
-      </c>
-      <c r="N14" t="n">
-        <v>9.19624266667517</v>
-      </c>
-      <c r="O14" t="n">
-        <v>128</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.641364134500748</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>78.996</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.012978134132977</v>
-      </c>
-      <c r="S14" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.906212526446624</v>
-      </c>
-      <c r="U14" t="n">
-        <v>8.326000000000001</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0.106765607686353</v>
-      </c>
-      <c r="W14" t="n">
-        <v>631.9299999999999</v>
-      </c>
-      <c r="X14" t="n">
-        <v>8.103337793086387</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1881.597</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>109年</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>9565.990664000001</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2093.197</v>
-      </c>
-      <c r="F15" t="n">
-        <v>21.88165422194479</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.003136110106494</v>
-      </c>
-      <c r="I15" t="n">
-        <v>5817.208664</v>
-      </c>
-      <c r="J15" t="n">
-        <v>60.81135627585429</v>
-      </c>
-      <c r="K15" t="n">
-        <v>937.115</v>
-      </c>
-      <c r="L15" t="n">
-        <v>9.796319408157851</v>
-      </c>
-      <c r="M15" t="n">
-        <v>809.115</v>
-      </c>
-      <c r="N15" t="n">
-        <v>8.458245762720304</v>
-      </c>
-      <c r="O15" t="n">
-        <v>128</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.338073645437545</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>86.23999999999999</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.901527118613546</v>
-      </c>
-      <c r="S15" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.738763004086494</v>
-      </c>
-      <c r="U15" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.162764114527051</v>
-      </c>
-      <c r="W15" t="n">
-        <v>631.9299999999999</v>
-      </c>
-      <c r="X15" t="n">
-        <v>6.606006865323029</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1862.443</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>110年</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11609.907294</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2093.937</v>
-      </c>
-      <c r="F16" t="n">
-        <v>18.03577709084849</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.038759999421577</v>
-      </c>
-      <c r="I16" t="n">
-        <v>7700.213294</v>
-      </c>
-      <c r="J16" t="n">
-        <v>66.32450284921283</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1094.168</v>
-      </c>
-      <c r="L16" t="n">
-        <v>9.424433566023959</v>
-      </c>
-      <c r="M16" t="n">
-        <v>824.968</v>
-      </c>
-      <c r="N16" t="n">
-        <v>7.105724267293188</v>
-      </c>
-      <c r="O16" t="n">
-        <v>269.2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.31870929873077</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>85.15900000000001</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.733502842387124</v>
-      </c>
-      <c r="S16" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.608704257582851</v>
-      </c>
-      <c r="U16" t="n">
-        <v>14.489</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.124798584804272</v>
-      </c>
-      <c r="W16" t="n">
-        <v>631.9299999999999</v>
-      </c>
-      <c r="X16" t="n">
-        <v>5.443023652106003</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1238.789</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>111年</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>14131.417164</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2097.98</v>
-      </c>
-      <c r="F17" t="n">
-        <v>14.84621093307355</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4.999</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.03537507910201</v>
-      </c>
-      <c r="I17" t="n">
-        <v>9723.747164</v>
-      </c>
-      <c r="J17" t="n">
-        <v>68.80942690426969</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1581.055</v>
-      </c>
-      <c r="L17" t="n">
-        <v>11.1882267832823</v>
-      </c>
-      <c r="M17" t="n">
-        <v>836.249</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.917658436482626</v>
-      </c>
-      <c r="O17" t="n">
-        <v>744.806</v>
-      </c>
-      <c r="P17" t="n">
-        <v>5.270568346799673</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>91.706</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.648951191063996</v>
-      </c>
-      <c r="S17" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.500091386305069</v>
-      </c>
-      <c r="U17" t="n">
-        <v>21.036</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.148859804758928</v>
-      </c>
-      <c r="W17" t="n">
-        <v>631.9299999999999</v>
-      </c>
-      <c r="X17" t="n">
-        <v>4.471809109208462</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>112年</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>17955.274284</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2103.654</v>
-      </c>
-      <c r="F18" t="n">
-        <v>11.71607833289727</v>
-      </c>
-      <c r="G18" t="n">
-        <v>7.289</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.040595314138394</v>
-      </c>
-      <c r="I18" t="n">
-        <v>12417.685284</v>
-      </c>
-      <c r="J18" t="n">
-        <v>69.15898408227291</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2677.422</v>
-      </c>
-      <c r="L18" t="n">
-        <v>14.91161848964824</v>
-      </c>
-      <c r="M18" t="n">
-        <v>914.183</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5.091445474685014</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1763.239</v>
-      </c>
-      <c r="P18" t="n">
-        <v>9.820173014963229</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>82.759</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.460917492492703</v>
-      </c>
-      <c r="S18" t="n">
-        <v>61.452</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.342250410815278</v>
-      </c>
-      <c r="U18" t="n">
-        <v>21.307</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.118667081677425</v>
-      </c>
-      <c r="W18" t="n">
-        <v>666.465</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.711806288550485</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>113年</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>21066.611146</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2122.6235</v>
-      </c>
-      <c r="F19" t="n">
-        <v>10.07577101646475</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7.489</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.035549144321781</v>
-      </c>
-      <c r="I19" t="n">
-        <v>14281.144946</v>
-      </c>
-      <c r="J19" t="n">
-        <v>67.79042365678077</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3905.0467</v>
-      </c>
-      <c r="L19" t="n">
-        <v>18.53666293518436</v>
-      </c>
-      <c r="M19" t="n">
-        <v>918.2037</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.358573353998338</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2986.843</v>
-      </c>
-      <c r="P19" t="n">
-        <v>14.17808958118602</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>83.842</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.397985226095178</v>
-      </c>
-      <c r="S19" t="n">
-        <v>61.452</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.291703300422233</v>
-      </c>
-      <c r="U19" t="n">
-        <v>22.39</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.106281925672945</v>
-      </c>
-      <c r="W19" t="n">
-        <v>666.465</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.163608021153152</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>114年</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>22872.010676</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2124.4215</v>
-      </c>
-      <c r="F20" t="n">
-        <v>9.288302327653216</v>
-      </c>
-      <c r="G20" t="n">
-        <v>7.489</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.032743076706668</v>
-      </c>
-      <c r="I20" t="n">
-        <v>15474.019976</v>
-      </c>
-      <c r="J20" t="n">
-        <v>67.65483015551912</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4517.1962</v>
-      </c>
-      <c r="L20" t="n">
-        <v>19.74988672395109</v>
-      </c>
-      <c r="M20" t="n">
-        <v>930.2602000000001</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.067242767493714</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3586.936</v>
-      </c>
-      <c r="P20" t="n">
-        <v>15.68264395645738</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>84.389</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.368961877446791</v>
-      </c>
-      <c r="S20" t="n">
-        <v>61.452</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.26867773398026</v>
-      </c>
-      <c r="U20" t="n">
-        <v>22.937</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0.10028414346653</v>
-      </c>
-      <c r="W20" t="n">
-        <v>664.495</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.905275838723118</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>再生能源</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>115年</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
